--- a/Grupo/RUN_Grupo.xlsx
+++ b/Grupo/RUN_Grupo.xlsx
@@ -461,13 +461,13 @@
         <v>29.77853952927232</v>
       </c>
       <c r="C2" s="2">
-        <v>115.8588091497623</v>
+        <v>115.8378505008696</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>34.50106128080613</v>
+        <v>34.49482010126083</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -492,7 +492,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>2.821414617771813</v>
+        <v>2.821414617771812</v>
       </c>
       <c r="C4" s="2">
         <v>105.3831300120735</v>
@@ -501,7 +501,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="2">
-        <v>2.973295034826117</v>
+        <v>2.973295034826116</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -512,13 +512,13 @@
         <v>30.18538127334559</v>
       </c>
       <c r="C5" s="2">
-        <v>110.4187482160855</v>
+        <v>110.4187482160854</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="2">
-        <v>33.33032014628088</v>
+        <v>33.33032014628087</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -546,13 +546,13 @@
         <v>2.159815414611264</v>
       </c>
       <c r="C7" s="2">
-        <v>111.1424640918352</v>
+        <v>111.1424640918351</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="2">
-        <v>2.400472071634245</v>
+        <v>2.400472071634244</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -586,7 +586,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="2">
-        <v>0.7542441810940009</v>
+        <v>0.7542441810940008</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -682,13 +682,13 @@
         <v>1.761997110075856</v>
       </c>
       <c r="C15" s="2">
-        <v>101.5835305559906</v>
+        <v>101.5835305559907</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="2">
-        <v>1.789898872709579</v>
+        <v>1.78989887270958</v>
       </c>
     </row>
   </sheetData>
